--- a/Analysed/GPT_gpt-5.4-2026-03-05_cot.xlsx
+++ b/Analysed/GPT_gpt-5.4-2026-03-05_cot.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H2" t="n">
-        <v>4.021728395061729</v>
+        <v>4.021446153846154</v>
       </c>
       <c r="I2" t="n">
-        <v>4.021745674654843</v>
+        <v>4.021466590494262</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9504643962848297</v>
+        <v>0.9475308641975309</v>
       </c>
     </row>
     <row r="3">
@@ -693,10 +693,10 @@
         <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>7.921400000000001</v>
+        <v>7.9228</v>
       </c>
       <c r="I6" t="n">
-        <v>8.050694007351167</v>
+        <v>8.052427460089286</v>
       </c>
       <c r="J6" t="n">
         <v>0.2653061224489796</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H8" t="n">
-        <v>5.108892215568862</v>
+        <v>5.111582089552239</v>
       </c>
       <c r="I8" t="n">
-        <v>5.116597946966149</v>
+        <v>5.119496826954191</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7784431137724551</v>
       </c>
     </row>
     <row r="9">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H9" t="n">
-        <v>5.017653631284916</v>
+        <v>5.017666666666666</v>
       </c>
       <c r="I9" t="n">
-        <v>5.017663437170243</v>
+        <v>5.017676421080446</v>
       </c>
       <c r="J9" t="n">
-        <v>0.949438202247191</v>
+        <v>0.9497206703910615</v>
       </c>
     </row>
     <row r="10">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>5.954915254237289</v>
+        <v>6.022333333333334</v>
       </c>
       <c r="I12" t="n">
-        <v>6.927813018575124</v>
+        <v>6.990089412875918</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.559322033898305</v>
       </c>
     </row>
     <row r="13">
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H26" t="n">
-        <v>1.310161290322581</v>
+        <v>1.30128</v>
       </c>
       <c r="I26" t="n">
-        <v>1.55018573288868</v>
+        <v>1.544076163924566</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2357723577235772</v>
+        <v>0.2419354838709677</v>
       </c>
     </row>
     <row r="27">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5186956521739131</v>
+        <v>0.5205714285714287</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6188757923661352</v>
+        <v>0.6193314367698678</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.7246376811594203</v>
       </c>
     </row>
     <row r="34">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H37" t="n">
-        <v>1.857142857142857</v>
+        <v>2.964999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>2.704493615131252</v>
+        <v>3.789733939649764</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5</v>
+        <v>0.4827586206896552</v>
       </c>
     </row>
     <row r="38">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H42" t="n">
-        <v>3.26304347826087</v>
+        <v>3.145999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>3.784700321259152</v>
+        <v>3.67059123303045</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.6530612244897959</v>
       </c>
     </row>
     <row r="43">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H43" t="n">
-        <v>2.968333333333333</v>
+        <v>2.69</v>
       </c>
       <c r="I43" t="n">
-        <v>3.554827234433013</v>
+        <v>3.315047510971751</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="H44" t="n">
-        <v>4.63159509202454</v>
+        <v>4.623939393939394</v>
       </c>
       <c r="I44" t="n">
-        <v>5.606787954403499</v>
+        <v>5.590077573050957</v>
       </c>
       <c r="J44" t="n">
-        <v>0.08307692307692308</v>
+        <v>0.09422492401215805</v>
       </c>
     </row>
     <row r="45">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>116</v>
+        <v>205</v>
       </c>
       <c r="H45" t="n">
-        <v>4.707068965517241</v>
+        <v>4.586829268292683</v>
       </c>
       <c r="I45" t="n">
-        <v>5.835552303737425</v>
+        <v>5.552627152320146</v>
       </c>
       <c r="J45" t="n">
-        <v>0.3826086956521739</v>
+        <v>0.4313725490196079</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="H46" t="n">
-        <v>4.889444444444445</v>
+        <v>4.707068965517241</v>
       </c>
       <c r="I46" t="n">
-        <v>6.158513078116611</v>
+        <v>5.835552303737425</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.3826086956521739</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="H47" t="n">
-        <v>2.266363636363637</v>
+        <v>4.889444444444445</v>
       </c>
       <c r="I47" t="n">
-        <v>2.896917797810757</v>
+        <v>6.158513078116611</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3483146067415731</v>
       </c>
     </row>
     <row r="48">
@@ -2534,20 +2534,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H48" t="n">
-        <v>5.71390243902439</v>
+        <v>2.266363636363637</v>
       </c>
       <c r="I48" t="n">
-        <v>7.109170134410907</v>
+        <v>2.896917797810757</v>
       </c>
       <c r="J48" t="n">
-        <v>0.225</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="49">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="H49" t="n">
-        <v>1.564031746031746</v>
+        <v>5.71390243902439</v>
       </c>
       <c r="I49" t="n">
-        <v>1.921359389797209</v>
+        <v>7.109170134410907</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9554140127388535</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="H50" t="n">
-        <v>1.83723076923077</v>
+        <v>1.564031746031746</v>
       </c>
       <c r="I50" t="n">
-        <v>2.251309818180496</v>
+        <v>1.921359389797209</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9329896907216495</v>
+        <v>0.9554140127388535</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
-        <v>1.417477477477477</v>
+        <v>1.881800000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>1.686123011767175</v>
+        <v>2.295694012711625</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9095477386934674</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="H52" t="n">
-        <v>3.222749999999999</v>
+        <v>1.417477477477477</v>
       </c>
       <c r="I52" t="n">
-        <v>3.808605387802731</v>
+        <v>1.686123011767175</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7721518987341772</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="53">
@@ -2754,20 +2754,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H53" t="n">
-        <v>3.182857142857144</v>
+        <v>3.222749999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>3.688296437685683</v>
+        <v>3.808605387802731</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.7721518987341772</v>
       </c>
     </row>
     <row r="54">
@@ -2798,19 +2798,63 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.129200000000001</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3.651911828070333</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.6326530612244898</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gpt-5.4-2026-03-05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>30</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>4.743333333333331</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>5.706955405467961</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>0.5862068965517241</v>
       </c>
     </row>
@@ -2857,14 +2901,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.6738</v>
+        <v>2.7233</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8669</v>
+        <v>1.8648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.6738 ± 1.8669</t>
+          <t>2.7233 ± 1.8648</t>
         </is>
       </c>
     </row>
@@ -2875,14 +2919,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.0804</v>
+        <v>3.1407</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9596</v>
+        <v>1.9713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0804 ± 1.9596</t>
+          <t>3.1407 ± 1.9713</t>
         </is>
       </c>
     </row>
@@ -2893,14 +2937,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6044</v>
+        <v>0.5978</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2755</v>
+        <v>0.2727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6044 ± 0.2755</t>
+          <t>0.5978 ± 0.2727</t>
         </is>
       </c>
     </row>
@@ -2975,19 +3019,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6251</v>
+        <v>4.6252</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0976</v>
+        <v>2.0981</v>
       </c>
       <c r="F2" t="n">
-        <v>4.757</v>
+        <v>4.7572</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7711</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>126.5</v>
+        <v>126.7</v>
       </c>
     </row>
     <row r="3">
@@ -3035,19 +3079,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6725</v>
+        <v>3.6842</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3012</v>
+        <v>2.3164</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0018</v>
+        <v>4.0126</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7074</v>
+        <v>0.7089</v>
       </c>
       <c r="H4" t="n">
-        <v>135.3</v>
+        <v>135.8</v>
       </c>
     </row>
     <row r="5">
@@ -3095,19 +3139,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6884</v>
+        <v>1.8734</v>
       </c>
       <c r="E6" t="n">
-        <v>0.622</v>
+        <v>0.8327</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1731</v>
+        <v>2.354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5109</v>
+        <v>0.5062</v>
       </c>
       <c r="H6" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="7">
@@ -3125,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0759</v>
+        <v>1.0744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2545</v>
+        <v>0.2527</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3756</v>
+        <v>1.3746</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3681</v>
+        <v>0.3691</v>
       </c>
       <c r="H7" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="8">
@@ -3155,19 +3199,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2522</v>
+        <v>2.1863</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7943</v>
+        <v>0.7109</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7078</v>
+        <v>2.6488</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7988</v>
+        <v>0.7748</v>
       </c>
       <c r="H8" t="n">
-        <v>129.3</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="9">
@@ -3185,19 +3229,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6613</v>
+        <v>2.6598</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3564</v>
+        <v>1.3462</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1771</v>
+        <v>3.1784</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7851</v>
+        <v>0.779</v>
       </c>
       <c r="H9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -3212,22 +3256,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4.4417</v>
+        <v>4.4646</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6019</v>
+        <v>1.2123</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5214</v>
+        <v>5.5238</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3411</v>
+        <v>0.358</v>
       </c>
       <c r="H10" t="n">
-        <v>125.6</v>
+        <v>139.5</v>
       </c>
     </row>
   </sheetData>
